--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שרון יפעת - Fly</v>
+        <v>צוף מימון &amp; יקיר - שקוף</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-01</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410667&amp;sid=9701017a4f3eb07f1a88060d082ee144</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410671&amp;sid=8d459752ae6e8897328a9b41efc340bd</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-01</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שרון יפעת - Fly</v>
+        <v>צוף מימון &amp; יקיר - שקוף</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>שירז - מאמי איפה עפת</v>
+        <v>אליאור נונה - מחרוזת עופר לוי 2026</v>
       </c>
       <c r="B3" t="str">
         <v>2026-05-01</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410666&amp;sid=9701017a4f3eb07f1a88060d082ee144</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410670&amp;sid=8d459752ae6e8897328a9b41efc340bd</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-01</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>שירז - מאמי איפה עפת</v>
+        <v>אליאור נונה - מחרוזת עופר לוי 2026</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>רות חתומה - תגיד לי &amp; Ya Ghayeb</v>
+        <v>אלשי שמואל - נכתב לנו מזמן</v>
       </c>
       <c r="B4" t="str">
         <v>2026-05-01</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410664&amp;sid=9701017a4f3eb07f1a88060d082ee144</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410669&amp;sid=8d459752ae6e8897328a9b41efc340bd</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-01</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>רות חתומה - תגיד לי &amp; Ya Ghayeb</v>
+        <v>אלשי שמואל - נכתב לנו מזמן</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>עידו כנפי - לבכות על כתפך</v>
+        <v>איציק מארי - עוף מדבר</v>
       </c>
       <c r="B5" t="str">
         <v>2026-05-01</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410662&amp;sid=9701017a4f3eb07f1a88060d082ee144</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410668&amp;sid=8d459752ae6e8897328a9b41efc340bd</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-01</v>
@@ -583,164 +583,12 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>עידו כנפי - לבכות על כתפך</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>ישי סוויסה &amp; מיכאל סוויסה &amp; שחר חסון - מה הדיבור</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410661&amp;sid=9701017a4f3eb07f1a88060d082ee144</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>ישי סוויסה &amp; מיכאל סוויסה &amp; שחר חסון - מה הדיבור</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>יהונתן שתיוי - גיב מי דאט</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410660&amp;sid=9701017a4f3eb07f1a88060d082ee144</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>יהונתן שתיוי - גיב מי דאט</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>איציק מארי - כותב עלייך שיר</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410659&amp;sid=9701017a4f3eb07f1a88060d082ee144</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>איציק מארי - כותב עלייך שיר</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>אביחי פרץ - משבר</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410656&amp;sid=9701017a4f3eb07f1a88060d082ee144</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-05-01</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>אביחי פרץ - משבר</v>
+        <v>איציק מארי - עוף מדבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>צוף מימון &amp; יקיר - שקוף</v>
+        <v>שי אוחיון - צדיקה קטנה שלי</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-03</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410671&amp;sid=8d459752ae6e8897328a9b41efc340bd</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410688&amp;sid=0c200ce49cd3193087f1d95a6c1b2a28</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>צוף מימון &amp; יקיר - שקוף</v>
+        <v>שי אוחיון - צדיקה קטנה שלי</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>אליאור נונה - מחרוזת עופר לוי 2026</v>
+        <v>צוקוש - דוקטור</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-03</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410670&amp;sid=8d459752ae6e8897328a9b41efc340bd</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410687&amp;sid=0c200ce49cd3193087f1d95a6c1b2a28</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>אליאור נונה - מחרוזת עופר לוי 2026</v>
+        <v>צוקוש - דוקטור</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>אלשי שמואל - נכתב לנו מזמן</v>
+        <v>פנינה רוזנבלום - אני תוצרת ישראל</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-03</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410669&amp;sid=8d459752ae6e8897328a9b41efc340bd</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410686&amp;sid=0c200ce49cd3193087f1d95a6c1b2a28</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>אלשי שמואל - נכתב לנו מזמן</v>
+        <v>פנינה רוזנבלום - אני תוצרת ישראל</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>איציק מארי - עוף מדבר</v>
+        <v>עמית אבני - הכחשה</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-03</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410668&amp;sid=8d459752ae6e8897328a9b41efc340bd</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410685&amp;sid=0c200ce49cd3193087f1d95a6c1b2a28</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-05-01</v>
+        <v>2026-05-03</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,12 +583,202 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>איציק מארי - עוף מדבר</v>
+        <v>עמית אבני - הכחשה</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>ליטל - למה זה ככה</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-05-03</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410684&amp;sid=0c200ce49cd3193087f1d95a6c1b2a28</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-05-03</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>ליטל - למה זה ככה</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>יזהר כהן - ששון ושמחה</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-05-03</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410682&amp;sid=0c200ce49cd3193087f1d95a6c1b2a28</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-05-03</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>יזהר כהן - ששון ושמחה</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>טדי פופי - הכתר שלי</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-05-03</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410681&amp;sid=0c200ce49cd3193087f1d95a6c1b2a28</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-05-03</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>טדי פופי - הכתר שלי</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>אנה זק - ילד שמנת</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-05-03</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410679&amp;sid=0c200ce49cd3193087f1d95a6c1b2a28</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-05-03</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>אנה זק - ילד שמנת</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>אחינועם - קיץ אחרון</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-05-03</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410678&amp;sid=0c200ce49cd3193087f1d95a6c1b2a28</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-05-03</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>אחינועם - קיץ אחרון</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שי אוחיון - צדיקה קטנה שלי</v>
+        <v>קולות ברדא - צונה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410688&amp;sid=0c200ce49cd3193087f1d95a6c1b2a28</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410701&amp;sid=eb6bc028a0e2344fefec44445bf4c699</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שי אוחיון - צדיקה קטנה שלי</v>
+        <v>קולות ברדא - צונה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>צוקוש - דוקטור</v>
+        <v>יואל אלהרר &amp; שמואל אלהרר - מול דרע</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410687&amp;sid=0c200ce49cd3193087f1d95a6c1b2a28</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410700&amp;sid=eb6bc028a0e2344fefec44445bf4c699</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>צוקוש - דוקטור</v>
+        <v>יואל אלהרר &amp; שמואל אלהרר - מול דרע</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>פנינה רוזנבלום - אני תוצרת ישראל</v>
+        <v>תעיזי &amp; רום לוף - ערסיתקלאסית</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410686&amp;sid=0c200ce49cd3193087f1d95a6c1b2a28</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410699&amp;sid=eb6bc028a0e2344fefec44445bf4c699</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>פנינה רוזנבלום - אני תוצרת ישראל</v>
+        <v>תעיזי &amp; רום לוף - ערסיתקלאסית</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>עמית אבני - הכחשה</v>
+        <v>שמעון טובול · מחרוזת ל''ג בעומר 2026</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410685&amp;sid=0c200ce49cd3193087f1d95a6c1b2a28</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410698&amp;sid=eb6bc028a0e2344fefec44445bf4c699</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>עמית אבני - הכחשה</v>
+        <v>שמעון טובול · מחרוזת ל''ג בעומר 2026</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ליטל - למה זה ככה</v>
+        <v>שיראל חדד - קח את זה בקלות</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410684&amp;sid=0c200ce49cd3193087f1d95a6c1b2a28</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410697&amp;sid=eb6bc028a0e2344fefec44445bf4c699</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>ליטל - למה זה ככה</v>
+        <v>שיראל חדד - קח את זה בקלות</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>יזהר כהן - ששון ושמחה</v>
+        <v>שימי לנגא - הנשמה בוערת</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410682&amp;sid=0c200ce49cd3193087f1d95a6c1b2a28</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410696&amp;sid=eb6bc028a0e2344fefec44445bf4c699</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>יזהר כהן - ששון ושמחה</v>
+        <v>שימי לנגא - הנשמה בוערת</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>טדי פופי - הכתר שלי</v>
+        <v>עמרם בוסקילה &amp; מימון מני כהן - רבי מאיר ענני</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410681&amp;sid=0c200ce49cd3193087f1d95a6c1b2a28</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410695&amp;sid=eb6bc028a0e2344fefec44445bf4c699</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,21 +697,21 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>טדי פופי - הכתר שלי</v>
+        <v>עמרם בוסקילה &amp; מימון מני כהן - רבי מאיר ענני</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>אנה זק - ילד שמנת</v>
+        <v>נינט טייב - כחול לבן</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410679&amp;sid=0c200ce49cd3193087f1d95a6c1b2a28</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410694&amp;sid=eb6bc028a0e2344fefec44445bf4c699</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -735,21 +735,21 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>אנה זק - ילד שמנת</v>
+        <v>נינט טייב - כחול לבן</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>אחינועם - קיץ אחרון</v>
+        <v>יקיר יהודה יאיר - בר יוחאי</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410678&amp;sid=0c200ce49cd3193087f1d95a6c1b2a28</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410693&amp;sid=eb6bc028a0e2344fefec44445bf4c699</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-05-03</v>
+        <v>2026-05-04</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -773,12 +773,164 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>אחינועם - קיץ אחרון</v>
+        <v>יקיר יהודה יאיר - בר יוחאי</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>יהודה שמעה - כה לחי</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410692&amp;sid=eb6bc028a0e2344fefec44445bf4c699</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>יהודה שמעה - כה לחי</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>דון יצחק מזרחי - מחרוזת רבי שמעון בר יוחאי 2026</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410691&amp;sid=eb6bc028a0e2344fefec44445bf4c699</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>דון יצחק מזרחי - מחרוזת רבי שמעון בר יוחאי 2026</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>אוראל דוד - שלבי התבודדות</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410690&amp;sid=eb6bc028a0e2344fefec44445bf4c699</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>אוראל דוד - שלבי התבודדות</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>אבי אבורומי - קח אותי לתאילנד</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410689&amp;sid=eb6bc028a0e2344fefec44445bf4c699</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>אבי אבורומי - קח אותי לתאילנד</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L14"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>קולות ברדא - צונה</v>
+        <v>מתנאל לוי - דרך חדשה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-04</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410701&amp;sid=eb6bc028a0e2344fefec44445bf4c699</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410710&amp;sid=b5c96900851e49a8a1ced3c2fd9ac5ca</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-04</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>קולות ברדא - צונה</v>
+        <v>מתנאל לוי - דרך חדשה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>יואל אלהרר &amp; שמואל אלהרר - מול דרע</v>
+        <v>קובי ברומר - בקודש הקדשים</v>
       </c>
       <c r="B3" t="str">
         <v>2026-05-04</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410700&amp;sid=eb6bc028a0e2344fefec44445bf4c699</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410709&amp;sid=b5c96900851e49a8a1ced3c2fd9ac5ca</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-04</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>יואל אלהרר &amp; שמואל אלהרר - מול דרע</v>
+        <v>קובי ברומר - בקודש הקדשים</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>תעיזי &amp; רום לוף - ערסיתקלאסית</v>
+        <v>עומרי זליג - מחרוזת שאגת טדי 2026</v>
       </c>
       <c r="B4" t="str">
         <v>2026-05-04</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410699&amp;sid=eb6bc028a0e2344fefec44445bf4c699</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410708&amp;sid=b5c96900851e49a8a1ced3c2fd9ac5ca</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-04</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>תעיזי &amp; רום לוף - ערסיתקלאסית</v>
+        <v>עומרי זליג - מחרוזת שאגת טדי 2026</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>שמעון טובול · מחרוזת ל''ג בעומר 2026</v>
+        <v>נריה אנג'ל - להיות רק בשמחה קאבר</v>
       </c>
       <c r="B5" t="str">
         <v>2026-05-04</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410698&amp;sid=eb6bc028a0e2344fefec44445bf4c699</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410707&amp;sid=b5c96900851e49a8a1ced3c2fd9ac5ca</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-04</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>שמעון טובול · מחרוזת ל''ג בעומר 2026</v>
+        <v>נריה אנג'ל - להיות רק בשמחה קאבר</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>שיראל חדד - קח את זה בקלות</v>
+        <v>מורדי השורה מארחים את נוי דקל - טבעות העשן</v>
       </c>
       <c r="B6" t="str">
         <v>2026-05-04</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410697&amp;sid=eb6bc028a0e2344fefec44445bf4c699</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410705&amp;sid=b5c96900851e49a8a1ced3c2fd9ac5ca</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-04</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>שיראל חדד - קח את זה בקלות</v>
+        <v>מורדי השורה מארחים את נוי דקל - טבעות העשן</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>שימי לנגא - הנשמה בוערת</v>
+        <v>דרור אלוני - מחרוזת חפלה בך בוטח 2026</v>
       </c>
       <c r="B7" t="str">
         <v>2026-05-04</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410696&amp;sid=eb6bc028a0e2344fefec44445bf4c699</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410704&amp;sid=b5c96900851e49a8a1ced3c2fd9ac5ca</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-04</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>שימי לנגא - הנשמה בוערת</v>
+        <v>דרור אלוני - מחרוזת חפלה בך בוטח 2026</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>עמרם בוסקילה &amp; מימון מני כהן - רבי מאיר ענני</v>
+        <v>אליסף חפץ - ברכת מזל טוב</v>
       </c>
       <c r="B8" t="str">
         <v>2026-05-04</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410695&amp;sid=eb6bc028a0e2344fefec44445bf4c699</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410703&amp;sid=b5c96900851e49a8a1ced3c2fd9ac5ca</v>
       </c>
       <c r="D8" t="str">
         <v>2026-05-04</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>עמרם בוסקילה &amp; מימון מני כהן - רבי מאיר ענני</v>
+        <v>אליסף חפץ - ברכת מזל טוב</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>נינט טייב - כחול לבן</v>
+        <v>אביב צורף - רשב''י</v>
       </c>
       <c r="B9" t="str">
         <v>2026-05-04</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410694&amp;sid=eb6bc028a0e2344fefec44445bf4c699</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410702&amp;sid=b5c96900851e49a8a1ced3c2fd9ac5ca</v>
       </c>
       <c r="D9" t="str">
         <v>2026-05-04</v>
@@ -735,202 +735,12 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>נינט טייב - כחול לבן</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>יקיר יהודה יאיר - בר יוחאי</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-05-04</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410693&amp;sid=eb6bc028a0e2344fefec44445bf4c699</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-05-04</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>יקיר יהודה יאיר - בר יוחאי</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>יהודה שמעה - כה לחי</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-05-04</v>
-      </c>
-      <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410692&amp;sid=eb6bc028a0e2344fefec44445bf4c699</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-05-04</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>יהודה שמעה - כה לחי</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>דון יצחק מזרחי - מחרוזת רבי שמעון בר יוחאי 2026</v>
-      </c>
-      <c r="B12" t="str">
-        <v>2026-05-04</v>
-      </c>
-      <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410691&amp;sid=eb6bc028a0e2344fefec44445bf4c699</v>
-      </c>
-      <c r="D12" t="str">
-        <v>2026-05-04</v>
-      </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J12" t="str">
-        <v/>
-      </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str">
-        <v>דון יצחק מזרחי - מחרוזת רבי שמעון בר יוחאי 2026</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>אוראל דוד - שלבי התבודדות</v>
-      </c>
-      <c r="B13" t="str">
-        <v>2026-05-04</v>
-      </c>
-      <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410690&amp;sid=eb6bc028a0e2344fefec44445bf4c699</v>
-      </c>
-      <c r="D13" t="str">
-        <v>2026-05-04</v>
-      </c>
-      <c r="E13" t="str">
-        <v/>
-      </c>
-      <c r="F13" t="str">
-        <v/>
-      </c>
-      <c r="G13" t="str">
-        <v/>
-      </c>
-      <c r="H13" t="str">
-        <v/>
-      </c>
-      <c r="I13" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J13" t="str">
-        <v/>
-      </c>
-      <c r="K13" t="str">
-        <v/>
-      </c>
-      <c r="L13" t="str">
-        <v>אוראל דוד - שלבי התבודדות</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>אבי אבורומי - קח אותי לתאילנד</v>
-      </c>
-      <c r="B14" t="str">
-        <v>2026-05-04</v>
-      </c>
-      <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410689&amp;sid=eb6bc028a0e2344fefec44445bf4c699</v>
-      </c>
-      <c r="D14" t="str">
-        <v>2026-05-04</v>
-      </c>
-      <c r="E14" t="str">
-        <v/>
-      </c>
-      <c r="F14" t="str">
-        <v/>
-      </c>
-      <c r="G14" t="str">
-        <v/>
-      </c>
-      <c r="H14" t="str">
-        <v/>
-      </c>
-      <c r="I14" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J14" t="str">
-        <v/>
-      </c>
-      <c r="K14" t="str">
-        <v/>
-      </c>
-      <c r="L14" t="str">
-        <v>אבי אבורומי - קח אותי לתאילנד</v>
+        <v>אביב צורף - רשב''י</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L24"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מתנאל לוי - דרך חדשה</v>
+        <v>תהילה זיאמר - פלסטר על הלב</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410710&amp;sid=b5c96900851e49a8a1ced3c2fd9ac5ca</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410735&amp;sid=31aae02b0bca367b27e8b26c3af186b6</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מתנאל לוי - דרך חדשה</v>
+        <v>תהילה זיאמר - פלסטר על הלב</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>קובי ברומר - בקודש הקדשים</v>
+        <v>רוחמה בן יוסף - יש סיכוי</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410709&amp;sid=b5c96900851e49a8a1ced3c2fd9ac5ca</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410734&amp;sid=31aae02b0bca367b27e8b26c3af186b6</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>קובי ברומר - בקודש הקדשים</v>
+        <v>רוחמה בן יוסף - יש סיכוי</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>עומרי זליג - מחרוזת שאגת טדי 2026</v>
+        <v>נתנאל אבקסיס - נקודות של אור</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410708&amp;sid=b5c96900851e49a8a1ced3c2fd9ac5ca</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410733&amp;sid=31aae02b0bca367b27e8b26c3af186b6</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>עומרי זליג - מחרוזת שאגת טדי 2026</v>
+        <v>נתנאל אבקסיס - נקודות של אור</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>נריה אנג'ל - להיות רק בשמחה קאבר</v>
+        <v>נריה קרמר - ניגונים</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410707&amp;sid=b5c96900851e49a8a1ced3c2fd9ac5ca</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410732&amp;sid=31aae02b0bca367b27e8b26c3af186b6</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>נריה אנג'ל - להיות רק בשמחה קאבר</v>
+        <v>נריה קרמר - ניגונים</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>מורדי השורה מארחים את נוי דקל - טבעות העשן</v>
+        <v>מתן חסן - לא מפחד</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410705&amp;sid=b5c96900851e49a8a1ced3c2fd9ac5ca</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410731&amp;sid=31aae02b0bca367b27e8b26c3af186b6</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>מורדי השורה מארחים את נוי דקל - טבעות העשן</v>
+        <v>מתן חסן - לא מפחד</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>דרור אלוני - מחרוזת חפלה בך בוטח 2026</v>
+        <v>טלי רבקה סימן טוב - לוקחת רגע</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410704&amp;sid=b5c96900851e49a8a1ced3c2fd9ac5ca</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410730&amp;sid=31aae02b0bca367b27e8b26c3af186b6</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>דרור אלוני - מחרוזת חפלה בך בוטח 2026</v>
+        <v>טלי רבקה סימן טוב - לוקחת רגע</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>אליסף חפץ - ברכת מזל טוב</v>
+        <v>דניאל ברזילאי &amp; הדר הלל - הדבש הזה</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410703&amp;sid=b5c96900851e49a8a1ced3c2fd9ac5ca</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410729&amp;sid=31aae02b0bca367b27e8b26c3af186b6</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,21 +697,21 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>אליסף חפץ - ברכת מזל טוב</v>
+        <v>דניאל ברזילאי &amp; הדר הלל - הדבש הזה</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>אביב צורף - רשב''י</v>
+        <v>איתי לוי - פרח קאבר</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410702&amp;sid=b5c96900851e49a8a1ced3c2fd9ac5ca</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410728&amp;sid=31aae02b0bca367b27e8b26c3af186b6</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-05-04</v>
+        <v>2026-05-05</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -735,12 +735,582 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>אביב צורף - רשב''י</v>
+        <v>איתי לוי - פרח קאבר</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>אורן כדורי - פאן פאן פאן</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410727&amp;sid=31aae02b0bca367b27e8b26c3af186b6</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>אורן כדורי - פאן פאן פאן</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>אדל חן - שיר חדש</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410726&amp;sid=31aae02b0bca367b27e8b26c3af186b6</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>אדל חן - שיר חדש</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>אבינועם כהן - פותח דף חדש</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410725&amp;sid=31aae02b0bca367b27e8b26c3af186b6</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>אבינועם כהן - פותח דף חדש</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>נעמי בניון - להיות בן אדם</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410724&amp;sid=31aae02b0bca367b27e8b26c3af186b6</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>נעמי בניון - להיות בן אדם</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>יגל אושרי - תגידי לי כן</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410723&amp;sid=31aae02b0bca367b27e8b26c3af186b6</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>יגל אושרי - תגידי לי כן</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>ששון שאולוב - נווה הדרים</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="C15" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410722&amp;sid=31aae02b0bca367b27e8b26c3af186b6</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>ששון שאולוב - נווה הדרים</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>שרית חדד - המזרח הרחוק</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="C16" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410721&amp;sid=31aae02b0bca367b27e8b26c3af186b6</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v>שרית חדד - המזרח הרחוק</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>עידו מלכה - טפטופים</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="C17" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410720&amp;sid=31aae02b0bca367b27e8b26c3af186b6</v>
+      </c>
+      <c r="D17" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <v>עידו מלכה - טפטופים</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>ינאי חיים לוי - פינה שקטה</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="C18" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410719&amp;sid=31aae02b0bca367b27e8b26c3af186b6</v>
+      </c>
+      <c r="D18" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
+        <v>ינאי חיים לוי - פינה שקטה</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>דנה ברגר - אם נותרנו נאהב</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="C19" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410718&amp;sid=31aae02b0bca367b27e8b26c3af186b6</v>
+      </c>
+      <c r="D19" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19" t="str">
+        <v>דנה ברגר - אם נותרנו נאהב</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>דיקלה - חולה מאהבה</v>
+      </c>
+      <c r="B20" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="C20" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410717&amp;sid=31aae02b0bca367b27e8b26c3af186b6</v>
+      </c>
+      <c r="D20" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
+      <c r="K20" t="str">
+        <v/>
+      </c>
+      <c r="L20" t="str">
+        <v>דיקלה - חולה מאהבה</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>גיל ויין &amp; נופיה - להרגיש אישה</v>
+      </c>
+      <c r="B21" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="C21" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410716&amp;sid=31aae02b0bca367b27e8b26c3af186b6</v>
+      </c>
+      <c r="D21" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J21" t="str">
+        <v/>
+      </c>
+      <c r="K21" t="str">
+        <v/>
+      </c>
+      <c r="L21" t="str">
+        <v>גיל ויין &amp; נופיה - להרגיש אישה</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>בר ניר - נרקיסיסט</v>
+      </c>
+      <c r="B22" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="C22" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410715&amp;sid=31aae02b0bca367b27e8b26c3af186b6</v>
+      </c>
+      <c r="D22" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J22" t="str">
+        <v/>
+      </c>
+      <c r="K22" t="str">
+        <v/>
+      </c>
+      <c r="L22" t="str">
+        <v>בר ניר - נרקיסיסט</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>אסף הרץ - תופס אותו</v>
+      </c>
+      <c r="B23" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="C23" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410714&amp;sid=31aae02b0bca367b27e8b26c3af186b6</v>
+      </c>
+      <c r="D23" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J23" t="str">
+        <v/>
+      </c>
+      <c r="K23" t="str">
+        <v/>
+      </c>
+      <c r="L23" t="str">
+        <v>אסף הרץ - תופס אותו</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>אור כהן - מגיע לי</v>
+      </c>
+      <c r="B24" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="C24" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410713&amp;sid=31aae02b0bca367b27e8b26c3af186b6</v>
+      </c>
+      <c r="D24" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J24" t="str">
+        <v/>
+      </c>
+      <c r="K24" t="str">
+        <v/>
+      </c>
+      <c r="L24" t="str">
+        <v>אור כהן - מגיע לי</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L24"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>דה לאון - נופל וקם</v>
+        <v>רון בי - להקת קיי פופ</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410737&amp;sid=26b28b5b14677093a961099e7541cc4f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410749&amp;sid=5c6057eda41f1133b96c7761082c80c1</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>דה לאון - נופל וקם</v>
+        <v>רון בי - להקת קיי פופ</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>אברהם איילאו - הכל בעצמך</v>
+        <v>רינת בר - אחת מאושרת</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410736&amp;sid=26b28b5b14677093a961099e7541cc4f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410748&amp;sid=5c6057eda41f1133b96c7761082c80c1</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-05</v>
+        <v>2026-05-06</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,12 +507,392 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>אברהם איילאו - הכל בעצמך</v>
+        <v>רינת בר - אחת מאושרת</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>רועי עומר - לא תדע (אהבה של אבא)</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410747&amp;sid=5c6057eda41f1133b96c7761082c80c1</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>רועי עומר - לא תדע (אהבה של אבא)</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>רון בי - להקת בנים</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410746&amp;sid=5c6057eda41f1133b96c7761082c80c1</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>רון בי - להקת בנים</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>עומרי אביב - לאן את הולכת</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410745&amp;sid=5c6057eda41f1133b96c7761082c80c1</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>עומרי אביב - לאן את הולכת</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>מושיק עפיה - אין לי</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410744&amp;sid=5c6057eda41f1133b96c7761082c80c1</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>מושיק עפיה - אין לי</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>דור הררי - גיבור על מדבקה</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410743&amp;sid=5c6057eda41f1133b96c7761082c80c1</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>דור הררי - גיבור על מדבקה</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>אלישבע - קפוא</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410742&amp;sid=5c6057eda41f1133b96c7761082c80c1</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>אלישבע - קפוא</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>איתן דרי - רכבת פרברים</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410741&amp;sid=5c6057eda41f1133b96c7761082c80c1</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>איתן דרי - רכבת פרברים</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>אילאי גואריהן - שריטות</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410740&amp;sid=5c6057eda41f1133b96c7761082c80c1</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>אילאי גואריהן - שריטות</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>אור קודאי - פירורים</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410739&amp;sid=5c6057eda41f1133b96c7761082c80c1</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>אור קודאי - פירורים</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>אבנר טואג - ככה תקבלו אותי</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410738&amp;sid=5c6057eda41f1133b96c7761082c80c1</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>אבנר טואג - ככה תקבלו אותי</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L13"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-05-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>רון בי - להקת קיי פופ</v>
+        <v>משה זאודה - מחרוזת 1 2026</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410749&amp;sid=5c6057eda41f1133b96c7761082c80c1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410762&amp;sid=3e551ab91bd1cab704747c4a2460e7d6</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>רון בי - להקת קיי פופ</v>
+        <v>משה זאודה - מחרוזת 1 2026</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>רינת בר - אחת מאושרת</v>
+        <v>ליאב מורחי - שלי לעולמים</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410748&amp;sid=5c6057eda41f1133b96c7761082c80c1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410761&amp;sid=3e551ab91bd1cab704747c4a2460e7d6</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>רינת בר - אחת מאושרת</v>
+        <v>ליאב מורחי - שלי לעולמים</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>רועי עומר - לא תדע (אהבה של אבא)</v>
+        <v>מתן לוי - ילדה אחת</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410747&amp;sid=5c6057eda41f1133b96c7761082c80c1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410760&amp;sid=3e551ab91bd1cab704747c4a2460e7d6</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>רועי עומר - לא תדע (אהבה של אבא)</v>
+        <v>מתן לוי - ילדה אחת</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>רון בי - להקת בנים</v>
+        <v>ליאב מורחי - קרוב אלייך</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410746&amp;sid=5c6057eda41f1133b96c7761082c80c1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410759&amp;sid=3e551ab91bd1cab704747c4a2460e7d6</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>רון בי - להקת בנים</v>
+        <v>ליאב מורחי - קרוב אלייך</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>עומרי אביב - לאן את הולכת</v>
+        <v>יניב סלמן - כמו אוויר</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410745&amp;sid=5c6057eda41f1133b96c7761082c80c1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410758&amp;sid=3e551ab91bd1cab704747c4a2460e7d6</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>עומרי אביב - לאן את הולכת</v>
+        <v>יניב סלמן - כמו אוויר</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>מושיק עפיה - אין לי</v>
+        <v>יהונתן מזרחי - בכל רגע תודה</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410744&amp;sid=5c6057eda41f1133b96c7761082c80c1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410757&amp;sid=3e551ab91bd1cab704747c4a2460e7d6</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>מושיק עפיה - אין לי</v>
+        <v>יהונתן מזרחי - בכל רגע תודה</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>דור הררי - גיבור על מדבקה</v>
+        <v>חן ביטון - ה' אוהב אותך</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410743&amp;sid=5c6057eda41f1133b96c7761082c80c1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410756&amp;sid=3e551ab91bd1cab704747c4a2460e7d6</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,21 +697,21 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>דור הררי - גיבור על מדבקה</v>
+        <v>חן ביטון - ה' אוהב אותך</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>אלישבע - קפוא</v>
+        <v>חיים דדון - שובי אליי</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410742&amp;sid=5c6057eda41f1133b96c7761082c80c1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410755&amp;sid=3e551ab91bd1cab704747c4a2460e7d6</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -735,21 +735,21 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>אלישבע - קפוא</v>
+        <v>חיים דדון - שובי אליי</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>איתן דרי - רכבת פרברים</v>
+        <v>בן חן - נפלו לי השמיים</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410741&amp;sid=5c6057eda41f1133b96c7761082c80c1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410754&amp;sid=3e551ab91bd1cab704747c4a2460e7d6</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -773,21 +773,21 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>איתן דרי - רכבת פרברים</v>
+        <v>בן חן - נפלו לי השמיים</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>אילאי גואריהן - שריטות</v>
+        <v>אליהו חזן &amp; אשר חזן - מחרוזת שירי שבת 2026</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410740&amp;sid=5c6057eda41f1133b96c7761082c80c1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410753&amp;sid=3e551ab91bd1cab704747c4a2460e7d6</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -811,21 +811,21 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>אילאי גואריהן - שריטות</v>
+        <v>אליהו חזן &amp; אשר חזן - מחרוזת שירי שבת 2026</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>אור קודאי - פירורים</v>
+        <v>אליאור זנדני - עיניים עצובות</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410739&amp;sid=5c6057eda41f1133b96c7761082c80c1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410752&amp;sid=3e551ab91bd1cab704747c4a2460e7d6</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -849,21 +849,21 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>אור קודאי - פירורים</v>
+        <v>אליאור זנדני - עיניים עצובות</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>אבנר טואג - ככה תקבלו אותי</v>
+        <v>אלי פרץ - מקנא בעצמי</v>
       </c>
       <c r="B13" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410738&amp;sid=5c6057eda41f1133b96c7761082c80c1</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410751&amp;sid=3e551ab91bd1cab704747c4a2460e7d6</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-05-06</v>
+        <v>2026-05-07</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -887,12 +887,50 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>אבנר טואג - ככה תקבלו אותי</v>
+        <v>אלי פרץ - מקנא בעצמי</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>אברהם אזן - זו התחלה</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-05-07</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410750&amp;sid=3e551ab91bd1cab704747c4a2460e7d6</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-05-07</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>אברהם אזן - זו התחלה</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L14"/>
   </ignoredErrors>
 </worksheet>
 </file>